--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_biotechnology.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-795.0000000000002</v>
+        <v>-24.01315789473685</v>
       </c>
       <c r="H2">
-        <v>-3485</v>
+        <v>-88.81578947368422</v>
       </c>
       <c r="I2">
-        <v>-3095</v>
+        <v>-76.48026315789474</v>
       </c>
       <c r="J2">
-        <v>-3095</v>
+        <v>-76.48026315789474</v>
       </c>
       <c r="K2">
-        <v>-59.7</v>
+        <v>-47.6</v>
       </c>
       <c r="L2">
-        <v>-2985</v>
+        <v>-78.28947368421053</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>92.40000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="V2">
-        <v>0.12516933080466</v>
+        <v>0.09133780094316207</v>
       </c>
       <c r="W2">
-        <v>-1.218367346938775</v>
+        <v>-0.4227353463587922</v>
       </c>
       <c r="X2">
-        <v>0.0701220067549702</v>
+        <v>0.1391025107126638</v>
       </c>
       <c r="Y2">
-        <v>-1.288489353693746</v>
+        <v>-0.5618378570714559</v>
       </c>
       <c r="Z2">
-        <v>0.0005698005698005699</v>
+        <v>0.007203791469194312</v>
       </c>
       <c r="AA2">
-        <v>-1.763532763532764</v>
+        <v>-0.5509478672985781</v>
       </c>
       <c r="AB2">
-        <v>0.06716043292033423</v>
+        <v>0.1295623139793635</v>
       </c>
       <c r="AC2">
-        <v>-1.830693196453098</v>
+        <v>-0.6805101812779417</v>
       </c>
       <c r="AD2">
-        <v>64.2</v>
+        <v>60.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>64.2</v>
+        <v>60.6</v>
       </c>
       <c r="AG2">
-        <v>-28.2</v>
+        <v>23.8</v>
       </c>
       <c r="AH2">
-        <v>0.08000997008973081</v>
+        <v>0.1307443365695793</v>
       </c>
       <c r="AI2">
-        <v>0.3631221719457013</v>
+        <v>0.505</v>
       </c>
       <c r="AJ2">
-        <v>-0.03971830985915493</v>
+        <v>0.0557768924302789</v>
       </c>
       <c r="AK2">
-        <v>-0.3341232227488152</v>
+        <v>0.2860576923076923</v>
       </c>
       <c r="AL2">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AM2">
-        <v>1.374</v>
+        <v>1.52</v>
       </c>
       <c r="AN2">
-        <v>-1.108808290155441</v>
+        <v>-1.402777777777778</v>
       </c>
       <c r="AO2">
-        <v>-41.54362416107382</v>
+        <v>-27.51479289940828</v>
       </c>
       <c r="AP2">
-        <v>0.4870466321243524</v>
+        <v>-0.550925925925926</v>
       </c>
       <c r="AQ2">
-        <v>-45.0509461426492</v>
+        <v>-30.59210526315789</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-795.0000000000002</v>
+        <v>-24.01315789473685</v>
       </c>
       <c r="H3">
-        <v>-3485</v>
+        <v>-88.81578947368422</v>
       </c>
       <c r="I3">
-        <v>-3095</v>
+        <v>-76.48026315789474</v>
       </c>
       <c r="J3">
-        <v>-3095</v>
+        <v>-76.48026315789474</v>
       </c>
       <c r="K3">
-        <v>-59.7</v>
+        <v>-47.6</v>
       </c>
       <c r="L3">
-        <v>-2985</v>
+        <v>-78.28947368421053</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>92.40000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="V3">
-        <v>0.12516933080466</v>
+        <v>0.09133780094316207</v>
       </c>
       <c r="W3">
-        <v>-1.218367346938775</v>
+        <v>-0.4227353463587922</v>
       </c>
       <c r="X3">
-        <v>0.0701220067549702</v>
+        <v>0.1391025107126638</v>
       </c>
       <c r="Y3">
-        <v>-1.288489353693746</v>
+        <v>-0.5618378570714559</v>
       </c>
       <c r="Z3">
-        <v>0.0005698005698005699</v>
+        <v>0.007203791469194312</v>
       </c>
       <c r="AA3">
-        <v>-1.763532763532764</v>
+        <v>-0.5509478672985781</v>
       </c>
       <c r="AB3">
-        <v>0.06716043292033423</v>
+        <v>0.1295623139793635</v>
       </c>
       <c r="AC3">
-        <v>-1.830693196453098</v>
+        <v>-0.6805101812779417</v>
       </c>
       <c r="AD3">
-        <v>64.2</v>
+        <v>60.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>64.2</v>
+        <v>60.6</v>
       </c>
       <c r="AG3">
-        <v>-28.2</v>
+        <v>23.8</v>
       </c>
       <c r="AH3">
-        <v>0.08000997008973081</v>
+        <v>0.1307443365695793</v>
       </c>
       <c r="AI3">
-        <v>0.3631221719457013</v>
+        <v>0.505</v>
       </c>
       <c r="AJ3">
-        <v>-0.03971830985915493</v>
+        <v>0.0557768924302789</v>
       </c>
       <c r="AK3">
-        <v>-0.3341232227488152</v>
+        <v>0.2860576923076923</v>
       </c>
       <c r="AL3">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AM3">
-        <v>1.374</v>
+        <v>1.52</v>
       </c>
       <c r="AN3">
-        <v>-1.108808290155441</v>
+        <v>-1.402777777777778</v>
       </c>
       <c r="AO3">
-        <v>-41.54362416107382</v>
+        <v>-27.51479289940828</v>
       </c>
       <c r="AP3">
-        <v>0.4870466321243524</v>
+        <v>-0.550925925925926</v>
       </c>
       <c r="AQ3">
-        <v>-45.0509461426492</v>
+        <v>-30.59210526315789</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_biotechnology.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-24.01315789473685</v>
+        <v>2.620320855614972</v>
       </c>
       <c r="H2">
-        <v>-88.81578947368422</v>
+        <v>-25.98930481283422</v>
       </c>
       <c r="I2">
-        <v>-76.48026315789474</v>
+        <v>-34.43850267379679</v>
       </c>
       <c r="J2">
-        <v>-76.48026315789474</v>
+        <v>-34.43850267379679</v>
       </c>
       <c r="K2">
-        <v>-47.6</v>
+        <v>-65.2</v>
       </c>
       <c r="L2">
-        <v>-78.28947368421053</v>
+        <v>-34.86631016042781</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>36.8</v>
+        <v>27.2</v>
       </c>
       <c r="V2">
-        <v>0.09133780094316207</v>
+        <v>0.09563994374120957</v>
       </c>
       <c r="W2">
-        <v>-0.4227353463587922</v>
+        <v>-1.097643097643098</v>
       </c>
       <c r="X2">
-        <v>0.1391025107126638</v>
+        <v>0.1144543850470864</v>
       </c>
       <c r="Y2">
-        <v>-0.5618378570714559</v>
+        <v>-1.212097482690184</v>
       </c>
       <c r="Z2">
-        <v>0.007203791469194312</v>
+        <v>0.02247596153846154</v>
       </c>
       <c r="AA2">
-        <v>-0.5509478672985781</v>
+        <v>-0.7740384615384616</v>
       </c>
       <c r="AB2">
-        <v>0.1295623139793635</v>
+        <v>0.105305493159686</v>
       </c>
       <c r="AC2">
-        <v>-0.6805101812779417</v>
+        <v>-0.8793439546981475</v>
       </c>
       <c r="AD2">
-        <v>60.6</v>
+        <v>57.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>60.6</v>
+        <v>57.5</v>
       </c>
       <c r="AG2">
-        <v>23.8</v>
+        <v>30.3</v>
       </c>
       <c r="AH2">
-        <v>0.1307443365695793</v>
+        <v>0.168177829774788</v>
       </c>
       <c r="AI2">
-        <v>0.505</v>
+        <v>0.5744255744255744</v>
       </c>
       <c r="AJ2">
-        <v>0.0557768924302789</v>
+        <v>0.09628217349857007</v>
       </c>
       <c r="AK2">
-        <v>0.2860576923076923</v>
+        <v>0.4156378600823045</v>
       </c>
       <c r="AL2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AM2">
-        <v>1.52</v>
+        <v>0.882</v>
       </c>
       <c r="AN2">
-        <v>-1.402777777777778</v>
+        <v>-0.9519867549668874</v>
       </c>
       <c r="AO2">
-        <v>-27.51479289940828</v>
+        <v>-37.88235294117648</v>
       </c>
       <c r="AP2">
-        <v>-0.550925925925926</v>
+        <v>-0.5016556291390729</v>
       </c>
       <c r="AQ2">
-        <v>-30.59210526315789</v>
+        <v>-73.01587301587303</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-24.01315789473685</v>
+        <v>2.620320855614972</v>
       </c>
       <c r="H3">
-        <v>-88.81578947368422</v>
+        <v>-25.98930481283422</v>
       </c>
       <c r="I3">
-        <v>-76.48026315789474</v>
+        <v>-34.43850267379679</v>
       </c>
       <c r="J3">
-        <v>-76.48026315789474</v>
+        <v>-34.43850267379679</v>
       </c>
       <c r="K3">
-        <v>-47.6</v>
+        <v>-65.2</v>
       </c>
       <c r="L3">
-        <v>-78.28947368421053</v>
+        <v>-34.86631016042781</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>36.8</v>
+        <v>27.2</v>
       </c>
       <c r="V3">
-        <v>0.09133780094316207</v>
+        <v>0.09563994374120957</v>
       </c>
       <c r="W3">
-        <v>-0.4227353463587922</v>
+        <v>-1.097643097643098</v>
       </c>
       <c r="X3">
-        <v>0.1391025107126638</v>
+        <v>0.1144543850470864</v>
       </c>
       <c r="Y3">
-        <v>-0.5618378570714559</v>
+        <v>-1.212097482690184</v>
       </c>
       <c r="Z3">
-        <v>0.007203791469194312</v>
+        <v>0.02247596153846154</v>
       </c>
       <c r="AA3">
-        <v>-0.5509478672985781</v>
+        <v>-0.7740384615384616</v>
       </c>
       <c r="AB3">
-        <v>0.1295623139793635</v>
+        <v>0.105305493159686</v>
       </c>
       <c r="AC3">
-        <v>-0.6805101812779417</v>
+        <v>-0.8793439546981475</v>
       </c>
       <c r="AD3">
-        <v>60.6</v>
+        <v>57.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>60.6</v>
+        <v>57.5</v>
       </c>
       <c r="AG3">
-        <v>23.8</v>
+        <v>30.3</v>
       </c>
       <c r="AH3">
-        <v>0.1307443365695793</v>
+        <v>0.168177829774788</v>
       </c>
       <c r="AI3">
-        <v>0.505</v>
+        <v>0.5744255744255744</v>
       </c>
       <c r="AJ3">
-        <v>0.0557768924302789</v>
+        <v>0.09628217349857007</v>
       </c>
       <c r="AK3">
-        <v>0.2860576923076923</v>
+        <v>0.4156378600823045</v>
       </c>
       <c r="AL3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AM3">
-        <v>1.52</v>
+        <v>0.882</v>
       </c>
       <c r="AN3">
-        <v>-1.402777777777778</v>
+        <v>-0.9519867549668874</v>
       </c>
       <c r="AO3">
-        <v>-27.51479289940828</v>
+        <v>-37.88235294117648</v>
       </c>
       <c r="AP3">
-        <v>-0.550925925925926</v>
+        <v>-0.5016556291390729</v>
       </c>
       <c r="AQ3">
-        <v>-30.59210526315789</v>
+        <v>-73.01587301587303</v>
       </c>
     </row>
   </sheetData>
